--- a/sheets/조재수대금교본/검수/칠갑산.xlsx
+++ b/sheets/조재수대금교본/검수/칠갑산.xlsx
@@ -5210,7 +5210,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -5228,14 +5228,14 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢⊏
+          <t xml:space="preserve">汰潢
 –</t>
         </is>
       </c>
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -5248,7 +5248,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -5293,11 +5293,7 @@
         </is>
       </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Z</t>
-        </is>
-      </c>
+      <c r="P4" s="21"/>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="119.22" customHeight="true">
@@ -5318,8 +5314,7 @@
       <c r="E5" s="24"/>
       <c r="F5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G5" s="24"/>
@@ -5330,16 +5325,11 @@
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="M5" s="24"/>
@@ -5392,7 +5382,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -5428,7 +5418,7 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–林ʒ</t>
+–林</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -5437,7 +5427,7 @@
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–И</t>
+–</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -5449,17 +5439,11 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
-潢
-ﾉ
-‹</t>
+潢</t>
         </is>
       </c>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
@@ -5470,23 +5454,20 @@
       <c r="G8" s="24"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I8" s="24"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑∼
-‹</t>
+          <t xml:space="preserve">姑∼</t>
         </is>
       </c>
       <c r="K8" s="24"/>
       <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-淋
-‹</t>
+淋</t>
         </is>
       </c>
       <c r="M8" s="24"/>
@@ -5497,18 +5478,14 @@
         </is>
       </c>
       <c r="O8" s="24"/>
-      <c r="P8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
     <row r="9" ht="119.22" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南∽</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -5521,7 +5498,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -5534,7 +5511,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-南∽</t>
+南</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -5604,8 +5581,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -5618,7 +5594,7 @@
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-∽南林</t>
+南林</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -5627,8 +5603,7 @@
       <c r="L11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
-汰
-‹</t>
+汰</t>
         </is>
       </c>
       <c r="M11" s="24"/>
@@ -5636,8 +5611,7 @@
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -5718,47 +5692,19 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
-      <c r="N14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N14" s="21"/>
       <c r="O14" s="24"/>
-      <c r="P14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P14" s="21"/>
       <c r="Q14" s="24"/>
     </row>
     <row r="15" ht="6.0" customHeight="true">
@@ -5791,13 +5737,13 @@
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -5815,13 +5761,13 @@
       <c r="I17" s="22"/>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="M17" s="22"/>
@@ -5834,7 +5780,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -5871,8 +5817,7 @@
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-ﾉ</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="C19" s="24"/>
@@ -5880,8 +5825,7 @@
       <c r="E19" s="24"/>
       <c r="F19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="G19" s="24"/>
@@ -5976,16 +5920,11 @@
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="C22" s="24"/>
-      <c r="D22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D22" s="21"/>
       <c r="E22" s="24"/>
       <c r="F22" s="21" t="inlineStr">
         <is>
@@ -5996,29 +5935,22 @@
       <c r="G22" s="24"/>
       <c r="H22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌
-‹</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="I22" s="24"/>
       <c r="J22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝
-‹</t>
+–</t>
         </is>
       </c>
       <c r="K22" s="24"/>
-      <c r="L22" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L22" s="21"/>
       <c r="M22" s="24"/>
       <c r="N22" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="O22" s="24"/>
@@ -6054,7 +5986,7 @@
       <c r="I23" s="22"/>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰⌝
+          <t xml:space="preserve">汰
 南</t>
         </is>
       </c>
@@ -6103,7 +6035,7 @@
       <c r="O24" s="23"/>
       <c r="P24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="Q24" s="23"/>
@@ -6112,28 +6044,20 @@
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
-      <c r="D25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="D25" s="21"/>
       <c r="E25" s="24"/>
       <c r="F25" s="21"/>
       <c r="G25" s="24"/>
       <c r="H25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-∽南林</t>
+南林</t>
         </is>
       </c>
       <c r="I25" s="24"/>
       <c r="J25" s="21"/>
       <c r="K25" s="24"/>
-      <c r="L25" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ</t>
-        </is>
-      </c>
+      <c r="L25" s="21"/>
       <c r="M25" s="24"/>
       <c r="N25" s="21"/>
       <c r="O25" s="24"/>
@@ -6214,41 +6138,17 @@
         </is>
       </c>
       <c r="C28" s="24"/>
-      <c r="D28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D28" s="21"/>
       <c r="E28" s="24"/>
-      <c r="F28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F28" s="21"/>
       <c r="G28" s="24"/>
-      <c r="H28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H28" s="21"/>
       <c r="I28" s="24"/>
-      <c r="J28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J28" s="21"/>
       <c r="K28" s="24"/>
-      <c r="L28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L28" s="21"/>
       <c r="M28" s="24"/>
-      <c r="N28" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N28" s="21"/>
       <c r="O28" s="24"/>
       <c r="P28" s="21" t="inlineStr">
         <is>

--- a/sheets/조재수대금교본/검수/칠갑산.xlsx
+++ b/sheets/조재수대금교본/검수/칠갑산.xlsx
@@ -5210,7 +5210,7 @@
       <c r="C3" s="22"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="E3" s="22"/>
@@ -5228,14 +5228,14 @@
       <c r="I3" s="22"/>
       <c r="J3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰潢
+          <t xml:space="preserve">汰潢⊏
 –</t>
         </is>
       </c>
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -5248,7 +5248,7 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
@@ -5293,7 +5293,11 @@
         </is>
       </c>
       <c r="O4" s="23"/>
-      <c r="P4" s="21"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Z</t>
+        </is>
+      </c>
       <c r="Q4" s="23"/>
     </row>
     <row r="5" ht="119.22" customHeight="true">
@@ -5325,7 +5329,11 @@
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21"/>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="K5" s="24"/>
       <c r="L5" s="21" t="inlineStr">
         <is>
@@ -5382,7 +5390,7 @@
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -5418,7 +5426,7 @@
       <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–林</t>
+–林ʒ</t>
         </is>
       </c>
       <c r="K7" s="23"/>
@@ -5427,7 +5435,7 @@
       <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-–</t>
+–И</t>
         </is>
       </c>
       <c r="O7" s="23"/>
@@ -5439,7 +5447,8 @@
       <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
-潢</t>
+潢
+ﾉ</t>
         </is>
       </c>
       <c r="C8" s="24"/>
@@ -5485,7 +5494,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南∽</t>
         </is>
       </c>
       <c r="C9" s="22"/>
@@ -5498,7 +5507,7 @@
       <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="G9" s="22"/>
@@ -5511,7 +5520,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-南</t>
+南∽</t>
         </is>
       </c>
       <c r="K9" s="22"/>
@@ -5581,7 +5590,7 @@
       <c r="C11" s="24"/>
       <c r="D11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢⊏∼</t>
         </is>
       </c>
       <c r="E11" s="24"/>
@@ -5594,7 +5603,7 @@
       <c r="H11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-南林</t>
+∽南林</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -5611,7 +5620,7 @@
       <c r="O11" s="24"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢⊏∼</t>
         </is>
       </c>
       <c r="Q11" s="24"/>
@@ -5737,13 +5746,13 @@
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="C17" s="22"/>
       <c r="D17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="E17" s="22"/>
@@ -5761,13 +5770,13 @@
       <c r="I17" s="22"/>
       <c r="J17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="K17" s="22"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="M17" s="22"/>
@@ -5780,7 +5789,7 @@
       <c r="O17" s="22"/>
       <c r="P17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="Q17" s="22"/>
@@ -5817,7 +5826,8 @@
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">淋
+ﾉ</t>
         </is>
       </c>
       <c r="C19" s="24"/>
@@ -5942,7 +5952,7 @@
       <c r="J22" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="K22" s="24"/>
@@ -5986,7 +5996,7 @@
       <c r="I23" s="22"/>
       <c r="J23" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰⌝
 南</t>
         </is>
       </c>
@@ -6035,7 +6045,7 @@
       <c r="O24" s="23"/>
       <c r="P24" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="Q24" s="23"/>
@@ -6044,20 +6054,28 @@
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
-      <c r="D25" s="21"/>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E25" s="24"/>
       <c r="F25" s="21"/>
       <c r="G25" s="24"/>
       <c r="H25" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南潢
-南林</t>
+∽南林</t>
         </is>
       </c>
       <c r="I25" s="24"/>
       <c r="J25" s="21"/>
       <c r="K25" s="24"/>
-      <c r="L25" s="21"/>
+      <c r="L25" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="M25" s="24"/>
       <c r="N25" s="21"/>
       <c r="O25" s="24"/>

--- a/sheets/조재수대금교본/검수/칠갑산.xlsx
+++ b/sheets/조재수대금교본/검수/칠갑산.xlsx
@@ -5155,28 +5155,28 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="80.0" customHeight="true">
+    <row r="2" ht="74.07" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
       <c r="P2" s="20"/>
       <c r="Q2" s="20"/>
     </row>
-    <row r="3" ht="119.22" customHeight="true">
+    <row r="3" ht="110.36" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -5253,7 +5253,7 @@
       </c>
       <c r="Q3" s="22"/>
     </row>
-    <row r="4" ht="119.22" customHeight="true">
+    <row r="4" ht="110.36" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -5300,7 +5300,7 @@
       </c>
       <c r="Q4" s="23"/>
     </row>
-    <row r="5" ht="119.22" customHeight="true">
+    <row r="5" ht="110.36" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
       </c>
       <c r="Q5" s="24"/>
     </row>
-    <row r="6" ht="119.22" customHeight="true">
+    <row r="6" ht="110.36" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -5408,7 +5408,7 @@
       </c>
       <c r="Q6" s="22"/>
     </row>
-    <row r="7" ht="119.22" customHeight="true">
+    <row r="7" ht="110.36" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21"/>
       <c r="C7" s="23"/>
@@ -5442,7 +5442,7 @@
       <c r="P7" s="21"/>
       <c r="Q7" s="23"/>
     </row>
-    <row r="8" ht="119.22" customHeight="true">
+    <row r="8" ht="110.36" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
       <c r="P8" s="21"/>
       <c r="Q8" s="24"/>
     </row>
-    <row r="9" ht="119.22" customHeight="true">
+    <row r="9" ht="110.36" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
       </c>
       <c r="Q9" s="22"/>
     </row>
-    <row r="10" ht="119.22" customHeight="true">
+    <row r="10" ht="110.36" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -5584,7 +5584,7 @@
       </c>
       <c r="Q10" s="23"/>
     </row>
-    <row r="11" ht="119.22" customHeight="true">
+    <row r="11" ht="110.36" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21"/>
       <c r="C11" s="24"/>
@@ -5625,7 +5625,7 @@
       </c>
       <c r="Q11" s="24"/>
     </row>
-    <row r="12" ht="119.22" customHeight="true">
+    <row r="12" ht="110.36" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="22"/>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="Q12" s="22"/>
     </row>
-    <row r="13" ht="119.22" customHeight="true">
+    <row r="13" ht="110.36" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -5692,7 +5692,7 @@
       <c r="P13" s="21"/>
       <c r="Q13" s="23"/>
     </row>
-    <row r="14" ht="119.22" customHeight="true">
+    <row r="14" ht="110.36" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5719,7 +5719,7 @@
     <row r="15" ht="6.0" customHeight="true">
       <c r="A15" s="0"/>
     </row>
-    <row r="16" ht="80.0" customHeight="true">
+    <row r="16" ht="74.07" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="20" t="inlineStr">
         <is>
@@ -5742,7 +5742,7 @@
       <c r="P16" s="20"/>
       <c r="Q16" s="20"/>
     </row>
-    <row r="17" ht="119.22" customHeight="true">
+    <row r="17" ht="110.36" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -5794,7 +5794,7 @@
       </c>
       <c r="Q17" s="22"/>
     </row>
-    <row r="18" ht="119.22" customHeight="true">
+    <row r="18" ht="110.36" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21"/>
       <c r="C18" s="23"/>
@@ -5822,7 +5822,7 @@
       <c r="P18" s="21"/>
       <c r="Q18" s="23"/>
     </row>
-    <row r="19" ht="119.22" customHeight="true">
+    <row r="19" ht="110.36" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
       <c r="P19" s="21"/>
       <c r="Q19" s="24"/>
     </row>
-    <row r="20" ht="119.22" customHeight="true">
+    <row r="20" ht="110.36" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
       <c r="P20" s="21"/>
       <c r="Q20" s="22"/>
     </row>
-    <row r="21" ht="119.22" customHeight="true">
+    <row r="21" ht="110.36" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21" t="inlineStr">
         <is>
@@ -5926,7 +5926,7 @@
       </c>
       <c r="Q21" s="23"/>
     </row>
-    <row r="22" ht="119.22" customHeight="true">
+    <row r="22" ht="110.36" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -5967,7 +5967,7 @@
       <c r="P22" s="21"/>
       <c r="Q22" s="24"/>
     </row>
-    <row r="23" ht="119.22" customHeight="true">
+    <row r="23" ht="110.36" customHeight="true">
       <c r="A23" s="0"/>
       <c r="B23" s="21" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="Q23" s="22"/>
     </row>
-    <row r="24" ht="119.22" customHeight="true">
+    <row r="24" ht="110.36" customHeight="true">
       <c r="A24" s="0"/>
       <c r="B24" s="21"/>
       <c r="C24" s="23"/>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="Q24" s="23"/>
     </row>
-    <row r="25" ht="119.22" customHeight="true">
+    <row r="25" ht="110.36" customHeight="true">
       <c r="A25" s="0"/>
       <c r="B25" s="21"/>
       <c r="C25" s="24"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="Q25" s="24"/>
     </row>
-    <row r="26" ht="119.22" customHeight="true">
+    <row r="26" ht="110.36" customHeight="true">
       <c r="A26" s="0"/>
       <c r="B26" s="21"/>
       <c r="C26" s="22"/>
@@ -6125,7 +6125,7 @@
       <c r="P26" s="21"/>
       <c r="Q26" s="22"/>
     </row>
-    <row r="27" ht="119.22" customHeight="true">
+    <row r="27" ht="110.36" customHeight="true">
       <c r="A27" s="0"/>
       <c r="B27" s="21"/>
       <c r="C27" s="23"/>
@@ -6148,7 +6148,7 @@
       <c r="P27" s="21"/>
       <c r="Q27" s="23"/>
     </row>
-    <row r="28" ht="119.22" customHeight="true">
+    <row r="28" ht="110.36" customHeight="true">
       <c r="A28" s="0"/>
       <c r="B28" s="21" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="50"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="54"/>
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="14" max="16383" man="1"/>
   </rowBreaks>
